--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,29 @@
         <is>
           <t>현재고</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -475,7 +475,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,29 @@
       </c>
       <c r="E2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,29 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,29 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,29 @@
         <v>50</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>70</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +593,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -521,7 +521,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HP-F8703</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -613,7 +613,7 @@
         <v>70</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -613,7 +613,7 @@
         <v>70</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">

--- a/filter_element.xlsx
+++ b/filter_element.xlsx
@@ -590,7 +590,7 @@
         <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
